--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Immunization, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -480,7 +480,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1622: fixed value = completed</t>
+    <t>++: fixed value = completed</t>
   </si>
   <si>
     <t>Observation.category</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -782,6 +782,9 @@
   </si>
   <si>
     <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFImmunizationReaction</t>
   </si>
   <si>
     <t>1595: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
@@ -4523,13 +4526,11 @@
         <v>40</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>40</v>
@@ -4580,15 +4581,15 @@
         <v>242</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4611,13 +4612,13 @@
         <v>40</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4668,7 +4669,7 @@
         <v>40</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>38</v>
@@ -4692,7 +4693,7 @@
         <v>40</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>40</v>
@@ -4706,10 +4707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4738,7 +4739,7 @@
         <v>98</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>100</v>
@@ -4779,10 +4780,10 @@
         <v>40</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>40</v>
@@ -4791,7 +4792,7 @@
         <v>237</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -4815,7 +4816,7 @@
         <v>40</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>40</v>
@@ -4829,10 +4830,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4855,19 +4856,19 @@
         <v>52</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>40</v>
@@ -4916,7 +4917,7 @@
         <v>40</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -4937,10 +4938,10 @@
         <v>40</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>40</v>
@@ -4954,10 +4955,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4980,19 +4981,19 @@
         <v>52</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>40</v>
@@ -5041,7 +5042,7 @@
         <v>40</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -5062,10 +5063,10 @@
         <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>40</v>
@@ -5074,15 +5075,15 @@
         <v>40</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5108,16 +5109,16 @@
         <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>40</v>
@@ -5142,13 +5143,13 @@
         <v>40</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>40</v>
@@ -5166,7 +5167,7 @@
         <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5175,7 +5176,7 @@
         <v>51</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>63</v>
@@ -5190,7 +5191,7 @@
         <v>94</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>40</v>
@@ -5204,14 +5205,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5233,16 +5234,16 @@
         <v>150</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>40</v>
@@ -5267,13 +5268,13 @@
         <v>40</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>40</v>
@@ -5291,7 +5292,7 @@
         <v>40</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -5309,19 +5310,19 @@
         <v>40</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>40</v>
@@ -5329,10 +5330,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5355,19 +5356,19 @@
         <v>40</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>40</v>
@@ -5416,7 +5417,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5437,10 +5438,10 @@
         <v>40</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>40</v>
@@ -5454,10 +5455,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5483,13 +5484,13 @@
         <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5518,10 +5519,10 @@
         <v>165</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>40</v>
@@ -5539,7 +5540,7 @@
         <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -5557,19 +5558,19 @@
         <v>40</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>40</v>
@@ -5577,10 +5578,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5606,16 +5607,16 @@
         <v>150</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>40</v>
@@ -5643,10 +5644,10 @@
         <v>165</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>40</v>
@@ -5664,7 +5665,7 @@
         <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5685,10 +5686,10 @@
         <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>40</v>
@@ -5702,10 +5703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5728,16 +5729,16 @@
         <v>40</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5787,7 +5788,7 @@
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -5805,19 +5806,19 @@
         <v>40</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>40</v>
@@ -5825,10 +5826,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5851,16 +5852,16 @@
         <v>40</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5910,7 +5911,7 @@
         <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -5928,19 +5929,19 @@
         <v>40</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>40</v>
@@ -5948,10 +5949,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5974,19 +5975,19 @@
         <v>40</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>40</v>
@@ -6035,7 +6036,7 @@
         <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -6047,7 +6048,7 @@
         <v>40</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>40</v>
@@ -6056,10 +6057,10 @@
         <v>40</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>40</v>
@@ -6073,10 +6074,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6099,13 +6100,13 @@
         <v>40</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6156,7 +6157,7 @@
         <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -6180,7 +6181,7 @@
         <v>40</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>40</v>
@@ -6194,10 +6195,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6226,7 +6227,7 @@
         <v>98</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>100</v>
@@ -6279,7 +6280,7 @@
         <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -6303,7 +6304,7 @@
         <v>40</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>40</v>
@@ -6317,14 +6318,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6346,10 +6347,10 @@
         <v>97</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>100</v>
@@ -6404,7 +6405,7 @@
         <v>40</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6442,10 +6443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6468,13 +6469,13 @@
         <v>40</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6525,7 +6526,7 @@
         <v>40</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>38</v>
@@ -6534,7 +6535,7 @@
         <v>51</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>63</v>
@@ -6546,10 +6547,10 @@
         <v>40</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>40</v>
@@ -6563,10 +6564,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6589,13 +6590,13 @@
         <v>40</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6646,7 +6647,7 @@
         <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
@@ -6655,7 +6656,7 @@
         <v>51</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>63</v>
@@ -6667,10 +6668,10 @@
         <v>40</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>40</v>
@@ -6684,10 +6685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6713,16 +6714,16 @@
         <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>40</v>
@@ -6750,10 +6751,10 @@
         <v>75</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>40</v>
@@ -6771,7 +6772,7 @@
         <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
@@ -6789,13 +6790,13 @@
         <v>40</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>40</v>
@@ -6809,10 +6810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6838,16 +6839,16 @@
         <v>150</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>40</v>
@@ -6875,10 +6876,10 @@
         <v>165</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>40</v>
@@ -6896,7 +6897,7 @@
         <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
@@ -6914,13 +6915,13 @@
         <v>40</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>40</v>
@@ -6934,10 +6935,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6960,17 +6961,17 @@
         <v>40</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>40</v>
@@ -7019,7 +7020,7 @@
         <v>40</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>38</v>
@@ -7043,7 +7044,7 @@
         <v>40</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>40</v>
@@ -7057,10 +7058,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7083,13 +7084,13 @@
         <v>40</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7140,7 +7141,7 @@
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -7161,10 +7162,10 @@
         <v>40</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>40</v>
@@ -7178,10 +7179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7204,16 +7205,16 @@
         <v>52</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7263,7 +7264,7 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7284,10 +7285,10 @@
         <v>40</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7301,10 +7302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7327,16 +7328,16 @@
         <v>52</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7386,7 +7387,7 @@
         <v>40</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -7407,10 +7408,10 @@
         <v>40</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>40</v>
@@ -7424,10 +7425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7450,19 +7451,19 @@
         <v>52</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>40</v>
@@ -7511,7 +7512,7 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -7532,10 +7533,10 @@
         <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
@@ -7549,10 +7550,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7575,13 +7576,13 @@
         <v>40</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7632,7 +7633,7 @@
         <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
@@ -7656,7 +7657,7 @@
         <v>40</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>40</v>
@@ -7670,10 +7671,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7702,7 +7703,7 @@
         <v>98</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>100</v>
@@ -7755,7 +7756,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -7779,7 +7780,7 @@
         <v>40</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>40</v>
@@ -7793,14 +7794,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7822,10 +7823,10 @@
         <v>97</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>100</v>
@@ -7880,7 +7881,7 @@
         <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
@@ -7918,10 +7919,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7947,13 +7948,13 @@
         <v>150</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>164</v>
@@ -8005,7 +8006,7 @@
         <v>40</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>51</v>
@@ -8023,7 +8024,7 @@
         <v>40</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>170</v>
@@ -8043,10 +8044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8072,13 +8073,13 @@
         <v>231</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>233</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>235</v>
@@ -8130,7 +8131,7 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -8148,7 +8149,7 @@
         <v>40</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>240</v>
@@ -8168,10 +8169,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8197,16 +8198,16 @@
         <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>40</v>
@@ -8231,13 +8232,13 @@
         <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>40</v>
@@ -8255,7 +8256,7 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
@@ -8264,7 +8265,7 @@
         <v>51</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>63</v>
@@ -8279,7 +8280,7 @@
         <v>94</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>40</v>
@@ -8293,14 +8294,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8322,16 +8323,16 @@
         <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>40</v>
@@ -8356,13 +8357,13 @@
         <v>40</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>40</v>
@@ -8380,7 +8381,7 @@
         <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -8398,19 +8399,19 @@
         <v>40</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>40</v>
@@ -8418,10 +8419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8447,16 +8448,16 @@
         <v>41</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>40</v>
@@ -8505,7 +8506,7 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -8526,10 +8527,10 @@
         <v>40</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>40</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,6 +124,135 @@
   </si>
   <si>
     <t>constraint</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: Workflow Pattern</t>
+  </si>
+  <si>
+    <t>Mapping: SNOMED CT Concept Domain Binding</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 v2 Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: SNOMED CT Attribute Binding</t>
+  </si>
+  <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -784,7 +913,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFImmunizationReaction</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
   </si>
   <si>
     <t>1595: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
@@ -1695,17 +1824,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ55"/>
+  <dimension ref="A1:AQ56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="111.11328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1713,6833 +1843,6964 @@
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="11.4375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.24609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.703125" customWidth="true"/>
+    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="16.3984375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="30.0703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="101.4296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" t="s" s="2">
+      <c r="A1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" t="s" s="2">
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="I1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="J1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="K1" t="s" s="2">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="N1" t="s" s="2">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="S1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="T1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="U1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="W1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="X1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Z1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AA1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AD1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AE1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AF1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="AG1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AH1" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AI1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AJ1" t="s" s="2">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="AK1" t="s" s="2">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="AL1" t="s" s="2">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="AM1" t="s" s="2">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="AN1" t="s" s="2">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="AO1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AQ1" t="s" s="2">
-        <v>40</v>
+      <c r="N1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="O1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="P1" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="Q1" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="R1" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="S1" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="T1" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="U1" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="V1" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="W1" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="AA1" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="AB1" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="AC1" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="AD1" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="AE1" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="AF1" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="AG1" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="AH1" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="AI1" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="AJ1" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="AK1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="AM1" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="AN1" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="N3" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>68</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O10" t="s" s="2">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>148</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>40</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>40</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>40</v>
+        <v>209</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>40</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="P19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>40</v>
+        <v>269</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>40</v>
+        <v>272</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>246</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>40</v>
+        <v>288</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>40</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>40</v>
+        <v>282</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>40</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>97</v>
+        <v>292</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>40</v>
+        <v>301</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>94</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>40</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>346</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>40</v>
+        <v>359</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>40</v>
+        <v>362</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>330</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>40</v>
+        <v>368</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>40</v>
+        <v>369</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>353</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>40</v>
+        <v>386</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>40</v>
+        <v>389</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>392</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>390</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>40</v>
+        <v>396</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>40</v>
+        <v>397</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>97</v>
+        <v>292</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>40</v>
+        <v>402</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>369</v>
+        <v>137</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>40</v>
+        <v>410</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>300</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="P43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>40</v>
+        <v>431</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>40</v>
+        <v>432</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>40</v>
+        <v>425</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>249</v>
+        <v>434</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>401</v>
+        <v>292</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>348</v>
+        <v>451</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>457</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>40</v>
+        <v>461</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>253</v>
+        <v>462</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>97</v>
+        <v>292</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>40</v>
+        <v>402</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>426</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>233</v>
+        <v>468</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>40</v>
+        <v>209</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>434</v>
+        <v>276</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Y53" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>40</v>
-      </c>
       <c r="AQ53" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>292</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>293</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>294</v>
+        <v>478</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="P54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>439</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="P55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="U55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="V55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>40</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -594,6 +594,10 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-38:++: fixed value "completed" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -669,6 +673,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-37:1594: fixed value "http://loinc.org|31044-1" {null}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -3579,36 +3587,36 @@
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3631,19 +3639,19 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3671,10 +3679,10 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -3692,7 +3700,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3716,10 +3724,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3730,14 +3738,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3756,19 +3764,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3793,13 +3801,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3817,7 +3825,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>94</v>
@@ -3829,36 +3837,36 @@
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3881,19 +3889,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3942,7 +3950,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3957,19 +3965,19 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -3980,10 +3988,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4006,16 +4014,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4065,7 +4073,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4086,13 +4094,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4103,14 +4111,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4129,19 +4137,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4190,7 +4198,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4205,19 +4213,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4228,14 +4236,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4254,19 +4262,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4315,7 +4323,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4330,19 +4338,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4353,10 +4361,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4379,16 +4387,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4438,7 +4446,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4459,13 +4467,13 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4476,10 +4484,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4502,17 +4510,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4561,7 +4569,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4576,19 +4584,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4599,10 +4607,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4625,19 +4633,19 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4674,17 +4682,17 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4693,7 +4701,7 @@
         <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
@@ -4702,19 +4710,19 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4722,13 +4730,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -4750,19 +4758,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4791,7 +4799,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4809,7 +4817,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4818,7 +4826,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4827,30 +4835,30 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4873,13 +4881,13 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4930,7 +4938,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4954,7 +4962,7 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4968,10 +4976,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5000,7 +5008,7 @@
         <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>143</v>
@@ -5041,19 +5049,19 @@
         <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5077,7 +5085,7 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5091,10 +5099,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5117,19 +5125,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5178,7 +5186,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5199,10 +5207,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5216,10 +5224,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5242,19 +5250,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5303,7 +5311,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5324,10 +5332,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5336,15 +5344,15 @@
         <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5367,19 +5375,19 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5404,13 +5412,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5428,7 +5436,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5437,7 +5445,7 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
@@ -5452,7 +5460,7 @@
         <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5466,14 +5474,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5492,19 +5500,19 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5529,13 +5537,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5553,7 +5561,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5571,19 +5579,19 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5591,10 +5599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5617,19 +5625,19 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5678,7 +5686,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5699,10 +5707,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5716,10 +5724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5742,16 +5750,16 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5777,13 +5785,13 @@
         <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -5801,7 +5809,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5819,19 +5827,19 @@
         <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -5839,10 +5847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5865,19 +5873,19 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5902,13 +5910,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5926,7 +5934,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5947,10 +5955,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5964,10 +5972,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5990,16 +5998,16 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6049,7 +6057,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6067,19 +6075,19 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6087,10 +6095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6113,16 +6121,16 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6172,7 +6180,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6190,19 +6198,19 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6210,10 +6218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6236,19 +6244,19 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6297,7 +6305,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6309,7 +6317,7 @@
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6318,10 +6326,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6335,10 +6343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6361,13 +6369,13 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6418,7 +6426,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6442,7 +6450,7 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6456,10 +6464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6488,7 +6496,7 @@
         <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>143</v>
@@ -6541,7 +6549,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6565,7 +6573,7 @@
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6579,14 +6587,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6608,10 +6616,10 @@
         <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>143</v>
@@ -6666,7 +6674,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6704,10 +6712,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6730,13 +6738,13 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6787,7 +6795,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6796,7 +6804,7 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>106</v>
@@ -6808,10 +6816,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6825,10 +6833,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6851,13 +6859,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6908,7 +6916,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6917,7 +6925,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6929,10 +6937,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6946,10 +6954,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6972,19 +6980,19 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7012,10 +7020,10 @@
         <v>118</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7033,7 +7041,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7051,13 +7059,13 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7071,10 +7079,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7097,19 +7105,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7134,13 +7142,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7158,7 +7166,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7176,13 +7184,13 @@
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7196,10 +7204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7222,17 +7230,17 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7281,7 +7289,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7305,7 +7313,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7319,10 +7327,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7345,13 +7353,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7402,7 +7410,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7423,10 +7431,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7440,10 +7448,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7466,16 +7474,16 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7525,7 +7533,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7546,10 +7554,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7563,10 +7571,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7589,16 +7597,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7648,7 +7656,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7669,10 +7677,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7686,10 +7694,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7712,19 +7720,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7773,7 +7781,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7794,10 +7802,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7811,10 +7819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7837,13 +7845,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7894,7 +7902,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7918,7 +7926,7 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7932,10 +7940,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7964,7 +7972,7 @@
         <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>143</v>
@@ -8017,7 +8025,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8041,7 +8049,7 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8055,14 +8063,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8084,10 +8092,10 @@
         <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>143</v>
@@ -8142,7 +8150,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8180,10 +8188,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8206,19 +8214,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8243,13 +8251,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8267,7 +8275,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8285,16 +8293,16 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8305,10 +8313,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8331,19 +8339,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8392,7 +8400,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8410,19 +8418,19 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>83</v>
@@ -8430,10 +8438,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8456,19 +8464,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8493,13 +8501,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8517,7 +8525,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8526,7 +8534,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8541,7 +8549,7 @@
         <v>137</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8555,14 +8563,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8581,19 +8589,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8618,13 +8626,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8642,7 +8650,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8660,19 +8668,19 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8680,10 +8688,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8709,16 +8717,16 @@
         <v>84</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8767,7 +8775,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8788,10 +8796,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-38:++: fixed value "completed" {null}</t>
+inv-44:++: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -676,7 +676,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-37:1594: fixed value "http://loinc.org|31044-1" {null}</t>
+inv-43:1594: fixed value = http://loinc.org|31044-1 {null}</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-44:++: fixed value = completed {null}</t>
+inv-42:++: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -676,7 +676,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-43:1594: fixed value = http://loinc.org|31044-1 {null}</t>
+inv-41:1594: fixed value = http://loinc.org|31044-1 {null}</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-42:++: fixed value = completed {null}</t>
+inv-44:++: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -676,7 +676,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-41:1594: fixed value = http://loinc.org|31044-1 {null}</t>
+inv-43:1594: fixed value = http://loinc.org|31044-1 {null}</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-44:++: fixed value = completed {null}</t>
+inv-44:++: fixed value = #completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -613,7 +613,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>++: fixed value = completed</t>
+    <t>++: fixed value = #completed</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -676,7 +676,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-43:1594: fixed value = http://loinc.org|31044-1 {null}</t>
+inv-45:++: fixed value = http://loinc.org|31044-1 {null}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -697,7 +697,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1594: fixed value = http://loinc.org|31044-1</t>
+    <t>++: fixed value = http://loinc.org|31044-1</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -924,7 +924,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
   </si>
   <si>
-    <t>1595: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>1594: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -997,6 +997,151 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>1595: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
@@ -1832,10 +1977,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ56"/>
+  <dimension ref="A1:AQ63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.37890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -5247,23 +5392,19 @@
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>294</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5311,7 +5452,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5323,7 +5464,7 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
@@ -5332,10 +5473,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5344,26 +5485,26 @@
         <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5375,20 +5516,18 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5412,43 +5551,43 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -5457,10 +5596,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5474,21 +5613,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5497,22 +5636,22 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5537,13 +5676,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5561,13 +5700,13 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -5579,19 +5718,19 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5599,10 +5738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5613,7 +5752,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5622,23 +5761,21 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5686,13 +5823,13 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
@@ -5707,10 +5844,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5724,10 +5861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5747,21 +5884,21 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5785,13 +5922,13 @@
         <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -5809,7 +5946,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5827,30 +5964,30 @@
         <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>364</v>
+        <v>83</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5870,22 +6007,20 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5910,13 +6045,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5934,7 +6069,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5955,10 +6090,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5972,10 +6107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5995,21 +6130,23 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6057,7 +6194,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6075,19 +6212,19 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6095,10 +6232,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6118,21 +6255,23 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>384</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6180,7 +6319,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6198,30 +6337,30 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6232,7 +6371,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6244,19 +6383,19 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>393</v>
+        <v>194</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6281,13 +6420,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6305,19 +6444,19 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>398</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6326,10 +6465,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>399</v>
+        <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6343,21 +6482,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6369,16 +6508,20 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6402,13 +6545,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6426,37 +6569,37 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>298</v>
+        <v>393</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6464,14 +6607,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6490,18 +6633,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>140</v>
+        <v>396</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>141</v>
+        <v>397</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6549,7 +6694,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6561,7 +6706,7 @@
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
@@ -6570,10 +6715,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>298</v>
+        <v>402</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6594,39 +6739,37 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6650,13 +6793,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6674,37 +6817,37 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6712,10 +6855,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6738,16 +6881,20 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>409</v>
+        <v>194</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6771,13 +6918,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6795,7 +6942,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6804,7 +6951,7 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>106</v>
@@ -6816,10 +6963,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6833,10 +6980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6859,15 +7006,17 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6916,7 +7065,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6925,7 +7074,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6934,19 +7083,19 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -6954,10 +7103,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6980,20 +7129,18 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7017,13 +7164,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7041,7 +7188,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7059,19 +7206,19 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>345</v>
+        <v>438</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>83</v>
+        <v>439</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7079,10 +7226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7105,19 +7252,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>194</v>
+        <v>441</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7142,13 +7289,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7166,7 +7313,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7178,19 +7325,19 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>446</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>426</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>345</v>
+        <v>448</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7204,10 +7351,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7230,18 +7377,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>436</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>437</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>438</v>
+        <v>296</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>439</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7289,7 +7434,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>435</v>
+        <v>297</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7301,7 +7446,7 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7313,7 +7458,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>440</v>
+        <v>298</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7327,21 +7472,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7353,15 +7498,17 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>294</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>442</v>
+        <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7410,19 +7557,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>441</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7431,10 +7578,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>444</v>
+        <v>298</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7448,14 +7595,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>452</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7468,24 +7615,26 @@
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>446</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7533,7 +7682,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7545,7 +7694,7 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7554,10 +7703,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>451</v>
+        <v>137</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7571,10 +7720,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7585,7 +7734,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7594,20 +7743,18 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7656,16 +7803,16 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7677,10 +7824,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7694,10 +7841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7708,7 +7855,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7717,23 +7864,19 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7781,16 +7924,16 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7802,10 +7945,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7819,10 +7962,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7845,16 +7988,20 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7878,13 +8025,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>473</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7902,7 +8049,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7914,19 +8061,19 @@
         <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>298</v>
+        <v>393</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7940,14 +8087,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7966,18 +8113,20 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>141</v>
+        <v>477</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>301</v>
+        <v>478</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -8001,13 +8150,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>83</v>
+        <v>481</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8025,7 +8174,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>304</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8037,19 +8186,19 @@
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>298</v>
+        <v>393</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8063,45 +8212,43 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>484</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>485</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>149</v>
+        <v>487</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8150,19 +8297,19 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -8174,7 +8321,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>137</v>
+        <v>488</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8188,10 +8335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8199,7 +8346,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>94</v>
@@ -8211,23 +8358,19 @@
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8251,13 +8394,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8275,10 +8418,10 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>94</v>
@@ -8293,16 +8436,16 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>472</v>
+        <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>215</v>
+        <v>461</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>216</v>
+        <v>492</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8313,10 +8456,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8327,7 +8470,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8339,20 +8482,18 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>276</v>
+        <v>494</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>278</v>
+        <v>496</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8400,13 +8541,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8418,19 +8559,19 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>285</v>
+        <v>498</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>286</v>
+        <v>499</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>83</v>
@@ -8438,10 +8579,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8452,7 +8593,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8461,23 +8602,21 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>194</v>
+        <v>501</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8501,13 +8640,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8525,16 +8664,16 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8546,10 +8685,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>137</v>
+        <v>498</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>334</v>
+        <v>505</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8563,14 +8702,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8586,22 +8725,22 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>194</v>
+        <v>441</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>507</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>508</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>339</v>
+        <v>509</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8626,13 +8765,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8650,7 +8789,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8668,19 +8807,19 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>344</v>
+        <v>511</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>345</v>
+        <v>512</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8688,10 +8827,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8702,7 +8841,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8714,20 +8853,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>483</v>
+        <v>295</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8775,39 +8910,912 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>482</v>
+        <v>297</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
+      <c r="H57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
+      <c r="AK59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1567,7 +1567,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file ? (#?) to Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$63</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Immunization {Observation}</t>
+    <t>Immunization Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ? (#?) to Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (#9000010.11) to Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -594,10 +597,6 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-44:++: fixed value = #completed {null}</t>
-  </si>
-  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -613,7 +612,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>++: fixed value = #completed</t>
+    <t>1674: fixed value = #completed</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -675,10 +674,6 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-45:++: fixed value = http://loinc.org|31044-1 {null}</t>
-  </si>
-  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -697,7 +692,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>++: fixed value = http://loinc.org|31044-1</t>
+    <t>1675: fixed value = http://loinc.org|31044-1</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1804,6 +1799,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2155,7 +2165,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2278,7 +2288,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>93</v>
       </c>
@@ -2401,7 +2411,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>101</v>
       </c>
@@ -2522,7 +2532,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>107</v>
       </c>
@@ -2645,7 +2655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>113</v>
       </c>
@@ -2768,7 +2778,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>122</v>
       </c>
@@ -2891,7 +2901,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>130</v>
       </c>
@@ -3014,7 +3024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>138</v>
       </c>
@@ -3137,7 +3147,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>146</v>
       </c>
@@ -3262,7 +3272,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>151</v>
       </c>
@@ -3385,7 +3395,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>160</v>
       </c>
@@ -3508,7 +3518,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>169</v>
       </c>
@@ -3631,7 +3641,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>178</v>
       </c>
@@ -3650,7 +3660,7 @@
         <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>95</v>
@@ -3732,36 +3742,36 @@
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AP14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>192</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3784,19 +3794,19 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3824,11 +3834,11 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
@@ -3845,7 +3855,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3869,28 +3879,28 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AP15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>203</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3900,7 +3910,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -3909,19 +3919,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3946,14 +3956,14 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
@@ -3970,7 +3980,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>94</v>
@@ -3982,36 +3992,36 @@
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AP16" t="s" s="2">
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AQ16" t="s" s="2">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4034,19 +4044,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4095,7 +4105,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4110,33 +4120,33 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4159,16 +4169,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4218,7 +4228,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4239,13 +4249,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4254,16 +4264,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4282,19 +4292,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4343,7 +4353,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4358,37 +4368,37 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4407,19 +4417,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4468,7 +4478,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4483,33 +4493,33 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4532,16 +4542,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4591,7 +4601,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4612,27 +4622,27 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO21" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4655,17 +4665,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4714,7 +4724,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4729,33 +4739,33 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AO22" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4778,19 +4788,19 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4827,17 +4837,17 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4846,7 +4856,7 @@
         <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
@@ -4855,33 +4865,33 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="B24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -4894,7 +4904,7 @@
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
@@ -4903,19 +4913,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4944,7 +4954,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4962,7 +4972,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4971,7 +4981,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4980,30 +4990,30 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AQ24" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>291</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5026,13 +5036,13 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5083,7 +5093,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5107,24 +5117,24 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5153,7 +5163,7 @@
         <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>143</v>
@@ -5194,19 +5204,19 @@
         <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5230,7 +5240,7 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5242,12 +5252,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5270,19 +5280,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5331,7 +5341,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5352,27 +5362,27 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="B28" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5395,13 +5405,13 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5452,7 +5462,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5476,7 +5486,7 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5488,12 +5498,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5522,7 +5532,7 @@
         <v>141</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>143</v>
@@ -5563,19 +5573,19 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5599,7 +5609,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5611,12 +5621,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5642,16 +5652,16 @@
         <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5700,7 +5710,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5721,27 +5731,27 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="B31" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5764,16 +5774,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5823,7 +5833,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5844,27 +5854,27 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="B32" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5878,7 +5888,7 @@
         <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>83</v>
@@ -5890,14 +5900,14 @@
         <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5946,7 +5956,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5967,27 +5977,27 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN32" t="s" s="2">
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
+      <c r="B33" t="s" s="2">
         <v>344</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6010,17 +6020,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6069,7 +6079,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6090,27 +6100,27 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="B34" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6133,19 +6143,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6194,7 +6204,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6215,27 +6225,27 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="B35" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6249,7 +6259,7 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>83</v>
@@ -6258,19 +6268,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6319,7 +6329,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6340,27 +6350,27 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AN35" t="s" s="2">
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6383,19 +6393,19 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6420,14 +6430,14 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6444,7 +6454,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6453,7 +6463,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6468,7 +6478,7 @@
         <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6480,16 +6490,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6508,19 +6518,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6545,13 +6555,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6569,7 +6579,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6587,30 +6597,30 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6633,19 +6643,19 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6694,7 +6704,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6715,27 +6725,27 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN38" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6758,16 +6768,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6793,13 +6803,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6817,7 +6827,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6835,30 +6845,30 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6881,19 +6891,19 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6918,13 +6928,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6942,7 +6952,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6963,27 +6973,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>422</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7006,16 +7016,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7065,7 +7075,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7083,30 +7093,30 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7129,16 +7139,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7188,7 +7198,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7206,30 +7216,30 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7252,19 +7262,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7313,7 +7323,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7325,36 +7335,36 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7377,13 +7387,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7434,7 +7444,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7458,7 +7468,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7470,12 +7480,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7504,7 +7514,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7557,7 +7567,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7581,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7593,16 +7603,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7624,10 +7634,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7682,7 +7692,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7718,12 +7728,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7746,13 +7756,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7803,7 +7813,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7812,7 +7822,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7824,27 +7834,27 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AN47" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7867,13 +7877,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7924,7 +7934,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7933,7 +7943,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7945,10 +7955,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7960,12 +7970,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7988,19 +7998,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8028,10 +8038,10 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8049,7 +8059,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8067,30 +8077,30 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8113,19 +8123,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8150,13 +8160,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8174,7 +8184,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8192,13 +8202,13 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8210,12 +8220,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8238,17 +8248,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8297,7 +8307,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8321,7 +8331,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8333,12 +8343,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8361,13 +8371,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8418,7 +8428,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8439,10 +8449,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8454,12 +8464,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8482,16 +8492,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8541,7 +8551,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8562,27 +8572,27 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8605,16 +8615,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8664,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8685,10 +8695,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8700,12 +8710,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8728,19 +8738,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8789,7 +8799,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8810,27 +8820,27 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AN55" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8853,13 +8863,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8910,7 +8920,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8934,7 +8944,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8946,12 +8956,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8980,7 +8990,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9033,7 +9043,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9057,7 +9067,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9069,16 +9079,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9100,10 +9110,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9158,7 +9168,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9194,12 +9204,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9222,19 +9232,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9259,14 +9269,14 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9283,7 +9293,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9301,17 +9311,17 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN59" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>217</v>
-      </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9319,12 +9329,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9347,19 +9357,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9408,7 +9418,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9426,30 +9436,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN60" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9472,19 +9482,19 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9509,14 +9519,14 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Y61" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9533,7 +9543,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9542,7 +9552,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9557,7 +9567,7 @@
         <v>137</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9569,16 +9579,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9597,19 +9607,19 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9634,13 +9644,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9658,7 +9668,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9676,30 +9686,30 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9725,16 +9735,16 @@
         <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9783,7 +9793,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9804,10 +9814,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9820,6 +9830,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ63">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI62">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="535">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,6 +591,9 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -668,6 +671,14 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="31044-1"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -695,7 +706,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1675: fixed value = http://loinc.org|31044-1</t>
+    <t>1675: fixed value = http://loinc.org#31044-1</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -3737,7 +3748,7 @@
         <v>84</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>84</v>
@@ -3752,13 +3763,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -3791,25 +3802,25 @@
         <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3817,10 +3828,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3843,19 +3854,19 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3883,10 +3894,10 @@
         <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
@@ -3904,7 +3915,7 @@
         <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3928,10 +3939,10 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>84</v>
@@ -3945,14 +3956,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3971,19 +3982,19 @@
         <v>96</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
@@ -3993,7 +4004,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -4008,13 +4019,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4032,7 +4043,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>95</v>
@@ -4047,25 +4058,25 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4073,10 +4084,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4099,19 +4110,19 @@
         <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -4160,7 +4171,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4175,19 +4186,19 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>84</v>
@@ -4201,10 +4212,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4227,16 +4238,16 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4286,7 +4297,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4307,13 +4318,13 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>84</v>
@@ -4327,14 +4338,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4353,19 +4364,19 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -4414,7 +4425,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4429,19 +4440,19 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>84</v>
@@ -4455,14 +4466,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4481,19 +4492,19 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4542,7 +4553,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4557,19 +4568,19 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>84</v>
@@ -4583,10 +4594,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4609,16 +4620,16 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4668,7 +4679,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4689,13 +4700,13 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
@@ -4709,10 +4720,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4735,17 +4746,17 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4794,7 +4805,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4809,19 +4820,19 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
@@ -4835,10 +4846,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4861,19 +4872,19 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4910,17 +4921,17 @@
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4929,7 +4940,7 @@
         <v>95</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>107</v>
@@ -4938,19 +4949,19 @@
         <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -4961,13 +4972,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -4989,19 +5000,19 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5026,11 +5037,11 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5048,7 +5059,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5057,7 +5068,7 @@
         <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>107</v>
@@ -5066,33 +5077,33 @@
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5115,13 +5126,13 @@
         <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5172,7 +5183,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5196,7 +5207,7 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
@@ -5213,10 +5224,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5245,7 +5256,7 @@
         <v>142</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>144</v>
@@ -5286,19 +5297,19 @@
         <v>84</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5322,7 +5333,7 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5339,10 +5350,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5365,19 +5376,19 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5426,7 +5437,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5447,10 +5458,10 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
@@ -5467,10 +5478,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5493,13 +5504,13 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5550,7 +5561,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5574,7 +5585,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
@@ -5591,10 +5602,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5623,7 +5634,7 @@
         <v>142</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>144</v>
@@ -5664,19 +5675,19 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5700,7 +5711,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5717,10 +5728,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5746,16 +5757,16 @@
         <v>109</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5804,7 +5815,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5825,10 +5836,10 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -5845,10 +5856,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5871,16 +5882,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5930,7 +5941,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5951,10 +5962,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -5971,10 +5982,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6000,14 +6011,14 @@
         <v>115</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6056,7 +6067,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6077,10 +6088,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6089,18 +6100,18 @@
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6123,17 +6134,17 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6182,7 +6193,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6203,10 +6214,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6223,10 +6234,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6249,19 +6260,19 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6310,7 +6321,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6331,10 +6342,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6351,10 +6362,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6377,19 +6388,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6438,7 +6449,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6459,10 +6470,10 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
@@ -6471,18 +6482,18 @@
         <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6505,19 +6516,19 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6542,13 +6553,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6566,7 +6577,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6575,7 +6586,7 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>107</v>
@@ -6590,7 +6601,7 @@
         <v>138</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6607,14 +6618,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6633,19 +6644,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6670,13 +6681,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6694,7 +6705,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6712,19 +6723,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6735,10 +6746,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6761,19 +6772,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6822,7 +6833,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6843,10 +6854,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6863,10 +6874,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6889,16 +6900,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6924,13 +6935,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6948,7 +6959,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6966,19 +6977,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6989,10 +7000,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7015,19 +7026,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7052,13 +7063,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7076,7 +7087,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7097,10 +7108,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7117,10 +7128,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7143,16 +7154,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7202,7 +7213,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7220,19 +7231,19 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7243,10 +7254,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7269,16 +7280,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7328,7 +7339,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7346,19 +7357,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7369,10 +7380,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7395,19 +7406,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7456,7 +7467,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7468,7 +7479,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7477,10 +7488,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7497,10 +7508,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7523,13 +7534,13 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7580,7 +7591,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7604,7 +7615,7 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7621,10 +7632,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7653,7 +7664,7 @@
         <v>142</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>144</v>
@@ -7706,7 +7717,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7730,7 +7741,7 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -7747,14 +7758,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7776,10 +7787,10 @@
         <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>144</v>
@@ -7834,7 +7845,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7875,10 +7886,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7901,13 +7912,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7958,7 +7969,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7967,7 +7978,7 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
@@ -7979,10 +7990,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7999,10 +8010,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8025,13 +8036,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8082,7 +8093,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8091,7 +8102,7 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
@@ -8103,10 +8114,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8123,10 +8134,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8149,19 +8160,19 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8189,10 +8200,10 @@
         <v>119</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8210,7 +8221,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8228,13 +8239,13 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8251,10 +8262,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8277,19 +8288,19 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8314,13 +8325,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8338,7 +8349,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8356,13 +8367,13 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8379,10 +8390,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8405,17 +8416,17 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8464,7 +8475,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8488,7 +8499,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8505,10 +8516,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8531,13 +8542,13 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8588,7 +8599,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8609,10 +8620,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8629,10 +8640,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8655,16 +8666,16 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8714,7 +8725,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8735,10 +8746,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8755,10 +8766,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8781,16 +8792,16 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8840,7 +8851,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8861,10 +8872,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8881,10 +8892,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8907,19 +8918,19 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8968,7 +8979,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8989,10 +9000,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9009,10 +9020,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9035,13 +9046,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9092,7 +9103,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9116,7 +9127,7 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9133,10 +9144,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9165,7 +9176,7 @@
         <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>144</v>
@@ -9218,7 +9229,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9242,7 +9253,7 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9259,14 +9270,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9288,10 +9299,10 @@
         <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>144</v>
@@ -9346,7 +9357,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9387,10 +9398,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9413,19 +9424,19 @@
         <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9450,13 +9461,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9474,7 +9485,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>95</v>
@@ -9492,16 +9503,16 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -9515,10 +9526,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9541,19 +9552,19 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9602,7 +9613,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9620,19 +9631,19 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9643,10 +9654,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9669,19 +9680,19 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9706,13 +9717,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9730,7 +9741,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9739,7 +9750,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -9754,7 +9765,7 @@
         <v>138</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9771,14 +9782,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9797,19 +9808,19 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9834,13 +9845,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9858,7 +9869,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9876,19 +9887,19 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9899,10 +9910,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9928,16 +9939,16 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9986,7 +9997,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10007,10 +10018,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -603,6 +603,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
+    <t>1674: fixed value = #completed</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -616,9 +619,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1674: fixed value = #completed</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -688,6 +688,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>1675: fixed value = http://loinc.org#31044-1</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -704,9 +707,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>1675: fixed value = http://loinc.org#31044-1</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1092,13 +1092,13 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1595: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
-  </si>
-  <si>
-    <t>1595: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
@@ -1177,13 +1177,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1596: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1596: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2042,14 +2042,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="101.4296875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="101.4296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2288,22 +2288,22 @@
         <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2925,13 +2925,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3051,13 +3051,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3177,13 +3177,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3305,13 +3305,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3422,25 +3422,25 @@
         <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3548,22 +3548,22 @@
         <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3674,22 +3674,22 @@
         <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3805,19 +3805,19 @@
         <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>193</v>
@@ -3939,16 +3939,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4061,25 +4061,25 @@
         <v>214</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AP16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AQ16" t="s" s="2">
+      <c r="AR16" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4186,25 +4186,25 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4318,19 +4318,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4440,25 +4440,25 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4568,25 +4568,25 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4700,19 +4700,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4820,25 +4820,25 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4949,25 +4949,25 @@
         <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5074,28 +5074,28 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5207,13 +5207,13 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5333,13 +5333,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5458,16 +5458,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5585,13 +5585,13 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5711,13 +5711,13 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5836,16 +5836,16 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5962,16 +5962,16 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6082,28 +6082,28 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP32" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -6214,16 +6214,16 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6342,16 +6342,16 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6464,28 +6464,28 @@
         <v>107</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>372</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP35" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6598,16 +6598,16 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6723,25 +6723,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6854,16 +6854,16 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6977,25 +6977,25 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -7108,16 +7108,16 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7231,25 +7231,25 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7357,25 +7357,25 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR42" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7488,16 +7488,16 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7615,13 +7615,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7741,13 +7741,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7869,13 +7869,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7990,16 +7990,16 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8114,16 +8114,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8239,19 +8239,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8367,19 +8367,19 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8499,13 +8499,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8620,16 +8620,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8746,16 +8746,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8872,16 +8872,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9000,16 +9000,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9127,13 +9127,13 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9253,13 +9253,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9381,13 +9381,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9503,22 +9503,22 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AO59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ59" t="s" s="2">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>84</v>
@@ -9631,25 +9631,25 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="AQ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9762,16 +9762,16 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9887,25 +9887,25 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10018,16 +10018,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (#9000010.11) to Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -933,7 +933,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
   </si>
   <si>
-    <t>1594: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>1594: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (9000010.11-.06)</t>
   </si>
   <si>
     <t>Immun.Immunization.Reaction</t>
@@ -1092,7 +1092,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1595: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>1595: source value from V IMMUNIZATION - REACTION (9000010.11-.06)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1177,7 +1177,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1596: source value from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>1596: source value from V IMMUNIZATION - REACTION (9000010.11-.06)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -2042,7 +2042,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="101.4296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.89453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="537">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1041,7 +1041,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://va.gov/terminology/vistaDefinedTerms/9000010.11-.06</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1595-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/9000010.11-.06</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -5745,7 +5751,7 @@
         <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -5776,7 +5782,7 @@
         <v>84</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>84</v>
@@ -5815,7 +5821,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5830,7 +5836,7 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
@@ -5842,10 +5848,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5856,10 +5862,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5885,13 +5891,13 @@
         <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5941,7 +5947,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5968,10 +5974,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5982,10 +5988,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6011,14 +6017,14 @@
         <v>115</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6067,7 +6073,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6082,7 +6088,7 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>293</v>
@@ -6094,10 +6100,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6108,10 +6114,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6137,14 +6143,14 @@
         <v>296</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6193,7 +6199,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6220,10 +6226,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6234,10 +6240,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6260,19 +6266,19 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6321,7 +6327,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6348,10 +6354,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6362,10 +6368,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6391,16 +6397,16 @@
         <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6449,7 +6455,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6464,7 +6470,7 @@
         <v>107</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>293</v>
@@ -6476,10 +6482,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6490,10 +6496,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6519,16 +6525,16 @@
         <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6553,13 +6559,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6577,7 +6583,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6586,7 +6592,7 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>107</v>
@@ -6607,7 +6613,7 @@
         <v>138</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6618,14 +6624,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6647,16 +6653,16 @@
         <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6681,13 +6687,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6705,7 +6711,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6729,27 +6735,27 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6772,19 +6778,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6833,7 +6839,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6860,10 +6866,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6874,10 +6880,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6903,13 +6909,13 @@
         <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6938,10 +6944,10 @@
         <v>211</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6959,7 +6965,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6983,27 +6989,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7029,16 +7035,16 @@
         <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7066,10 +7072,10 @@
         <v>211</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7087,7 +7093,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7114,10 +7120,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7128,10 +7134,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7154,16 +7160,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7213,7 +7219,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7237,27 +7243,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7280,16 +7286,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7339,7 +7345,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7363,27 +7369,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7406,19 +7412,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7467,7 +7473,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7479,7 +7485,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7494,10 +7500,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7508,10 +7514,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7632,10 +7638,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7758,14 +7764,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7787,10 +7793,10 @@
         <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>144</v>
@@ -7845,7 +7851,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7886,10 +7892,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7912,13 +7918,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7969,7 +7975,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7978,7 +7984,7 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
@@ -7996,10 +8002,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8010,10 +8016,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8036,13 +8042,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8093,7 +8099,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8102,7 +8108,7 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
@@ -8120,10 +8126,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8134,10 +8140,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8163,16 +8169,16 @@
         <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8200,10 +8206,10 @@
         <v>119</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8221,7 +8227,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8245,13 +8251,13 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8262,10 +8268,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8291,16 +8297,16 @@
         <v>195</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8328,10 +8334,10 @@
         <v>211</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8349,7 +8355,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8373,13 +8379,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8390,10 +8396,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8416,17 +8422,17 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8475,7 +8481,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8505,7 +8511,7 @@
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8516,10 +8522,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8545,10 +8551,10 @@
         <v>296</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8599,7 +8605,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8626,10 +8632,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8640,10 +8646,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8666,16 +8672,16 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8725,7 +8731,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8752,10 +8758,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8766,10 +8772,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8792,16 +8798,16 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8851,7 +8857,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8878,10 +8884,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8892,10 +8898,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8918,19 +8924,19 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8979,7 +8985,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9006,10 +9012,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9020,10 +9026,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9144,10 +9150,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9270,14 +9276,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9299,10 +9305,10 @@
         <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>144</v>
@@ -9357,7 +9363,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9398,10 +9404,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9427,13 +9433,13 @@
         <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>209</v>
@@ -9485,7 +9491,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>95</v>
@@ -9509,7 +9515,7 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>217</v>
@@ -9526,10 +9532,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9555,13 +9561,13 @@
         <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>279</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>281</v>
@@ -9613,7 +9619,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9637,7 +9643,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>286</v>
@@ -9654,10 +9660,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9683,16 +9689,16 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9717,13 +9723,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9741,7 +9747,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9750,7 +9756,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -9771,7 +9777,7 @@
         <v>138</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9782,14 +9788,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9811,16 +9817,16 @@
         <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9845,13 +9851,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9869,7 +9875,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9893,27 +9899,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9939,16 +9945,16 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9997,7 +10003,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10024,10 +10030,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1585,7 +1585,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -930,7 +930,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
+    <t>http://va.gov/fhir/ValueSet/ImmunizationReaction</t>
   </si>
   <si>
     <t>1594: terminologyMaps using VF_ImmunizationReaction on V IMMUNIZATION - REACTION (9000010.11-.06)</t>
@@ -2038,7 +2038,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2056,7 +2056,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.89453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -942,7 +942,7 @@
     <t>Immun.Immunization.Reaction</t>
   </si>
   <si>
-    <t>immunization.reaction</t>
+    <t>Vaccination.VaccinationExtension.Reaction</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -942,7 +942,7 @@
     <t>Immun.Immunization.Reaction</t>
   </si>
   <si>
-    <t>Vaccination.VaccinationExtension.Reaction</t>
+    <t>Vaccination.Extension[VaccinationExtension].Reaction</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to Observation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1104,7 +1104,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1595: source value from V IMMUNIZATION - REACTION (9000010.11-.06)</t>
+    <t>1595: source value based on V IMMUNIZATION - REACTION (9000010.11-.06)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1189,7 +1189,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1596: source value from V IMMUNIZATION - REACTION (9000010.11-.06)</t>
+    <t>1596: source value based on V IMMUNIZATION - REACTION (9000010.11-.06)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,6 +931,9 @@
   </si>
   <si>
     <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>see mapping [VF_ImmunizationReaction](ConceptMap-VF-ImmunizationReaction.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/ImmunizationReaction</t>
@@ -2043,7 +2046,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.59765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -5121,9 +5124,11 @@
       <c r="X24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5156,13 +5161,13 @@
         <v>108</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>85</v>
@@ -5185,10 +5190,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5211,13 +5216,13 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5268,7 +5273,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5301,7 +5306,7 @@
         <v>85</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>85</v>
@@ -5312,10 +5317,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5344,7 +5349,7 @@
         <v>143</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>145</v>
@@ -5385,10 +5390,10 @@
         <v>85</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>85</v>
@@ -5397,7 +5402,7 @@
         <v>284</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5430,7 +5435,7 @@
         <v>85</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>85</v>
@@ -5441,10 +5446,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5467,19 +5472,19 @@
         <v>97</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>85</v>
@@ -5528,7 +5533,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5558,10 +5563,10 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>85</v>
@@ -5572,10 +5577,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5598,13 +5603,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5655,7 +5660,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5688,7 +5693,7 @@
         <v>85</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5699,10 +5704,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5731,7 +5736,7 @@
         <v>143</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>145</v>
@@ -5772,10 +5777,10 @@
         <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>85</v>
@@ -5784,7 +5789,7 @@
         <v>284</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5817,7 +5822,7 @@
         <v>85</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>85</v>
@@ -5828,10 +5833,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5857,16 +5862,16 @@
         <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -5876,7 +5881,7 @@
         <v>85</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>85</v>
@@ -5915,7 +5920,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5930,7 +5935,7 @@
         <v>108</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>85</v>
@@ -5945,10 +5950,10 @@
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>85</v>
@@ -5959,10 +5964,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5985,16 +5990,16 @@
         <v>97</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6044,7 +6049,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6074,10 +6079,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6088,10 +6093,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6117,14 +6122,14 @@
         <v>116</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -6173,7 +6178,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6188,13 +6193,13 @@
         <v>108</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>85</v>
@@ -6203,10 +6208,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6217,10 +6222,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6243,17 +6248,17 @@
         <v>97</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6302,7 +6307,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6332,10 +6337,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6346,10 +6351,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6372,19 +6377,19 @@
         <v>97</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6433,7 +6438,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6463,10 +6468,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6477,10 +6482,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6503,19 +6508,19 @@
         <v>97</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6564,7 +6569,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6579,13 +6584,13 @@
         <v>108</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>85</v>
@@ -6594,10 +6599,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6608,10 +6613,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6637,16 +6642,16 @@
         <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6671,13 +6676,13 @@
         <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>85</v>
@@ -6695,7 +6700,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6704,7 +6709,7 @@
         <v>96</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>108</v>
@@ -6728,7 +6733,7 @@
         <v>139</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -6739,14 +6744,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6768,16 +6773,16 @@
         <v>196</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6802,13 +6807,13 @@
         <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>85</v>
@@ -6826,7 +6831,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6853,27 +6858,27 @@
         <v>85</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6896,19 +6901,19 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>85</v>
@@ -6957,7 +6962,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6987,10 +6992,10 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
@@ -7001,10 +7006,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7030,13 +7035,13 @@
         <v>196</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7065,10 +7070,10 @@
         <v>212</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
@@ -7086,7 +7091,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7113,27 +7118,27 @@
         <v>85</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7159,16 +7164,16 @@
         <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7196,10 +7201,10 @@
         <v>212</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7217,7 +7222,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7247,10 +7252,10 @@
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
@@ -7261,10 +7266,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7287,16 +7292,16 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7346,7 +7351,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7373,27 +7378,27 @@
         <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7416,16 +7421,16 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7475,7 +7480,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7502,27 +7507,27 @@
         <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7545,19 +7550,19 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7606,7 +7611,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7618,7 +7623,7 @@
         <v>85</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>85</v>
@@ -7636,10 +7641,10 @@
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
@@ -7650,10 +7655,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7676,13 +7681,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7733,7 +7738,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7766,7 +7771,7 @@
         <v>85</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7777,10 +7782,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7809,7 +7814,7 @@
         <v>143</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>145</v>
@@ -7862,7 +7867,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7895,7 +7900,7 @@
         <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -7906,14 +7911,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7935,10 +7940,10 @@
         <v>142</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>145</v>
@@ -7993,7 +7998,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8037,10 +8042,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8063,13 +8068,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8120,7 +8125,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8129,7 +8134,7 @@
         <v>96</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>108</v>
@@ -8150,10 +8155,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8164,10 +8169,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8190,13 +8195,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8247,7 +8252,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8256,7 +8261,7 @@
         <v>96</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>108</v>
@@ -8277,10 +8282,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8291,10 +8296,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8320,16 +8325,16 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8357,10 +8362,10 @@
         <v>120</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8378,7 +8383,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8405,13 +8410,13 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8422,10 +8427,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8451,16 +8456,16 @@
         <v>196</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8488,10 +8493,10 @@
         <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8509,7 +8514,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8536,13 +8541,13 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8553,10 +8558,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8579,17 +8584,17 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8638,7 +8643,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8671,7 +8676,7 @@
         <v>85</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8682,10 +8687,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8708,13 +8713,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8765,7 +8770,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8795,10 +8800,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -8809,10 +8814,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8835,16 +8840,16 @@
         <v>97</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8894,7 +8899,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8924,10 +8929,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -8938,10 +8943,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8964,16 +8969,16 @@
         <v>97</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9023,7 +9028,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9053,10 +9058,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9067,10 +9072,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9093,19 +9098,19 @@
         <v>97</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9154,7 +9159,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9184,10 +9189,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9198,10 +9203,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9224,13 +9229,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9281,7 +9286,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9314,7 +9319,7 @@
         <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9325,10 +9330,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9357,7 +9362,7 @@
         <v>143</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>145</v>
@@ -9410,7 +9415,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9443,7 +9448,7 @@
         <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9454,14 +9459,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9483,10 +9488,10 @@
         <v>142</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>145</v>
@@ -9541,7 +9546,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9585,10 +9590,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9614,13 +9619,13 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>210</v>
@@ -9672,7 +9677,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>96</v>
@@ -9699,7 +9704,7 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>218</v>
@@ -9716,10 +9721,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9745,13 +9750,13 @@
         <v>278</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>280</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>282</v>
@@ -9803,7 +9808,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9830,7 +9835,7 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>287</v>
@@ -9847,10 +9852,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9876,16 +9881,16 @@
         <v>196</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -9910,13 +9915,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -9934,7 +9939,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9943,7 +9948,7 @@
         <v>96</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>108</v>
@@ -9967,7 +9972,7 @@
         <v>139</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -9978,14 +9983,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10007,16 +10012,16 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10041,13 +10046,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10065,7 +10070,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10092,27 +10097,27 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10138,16 +10143,16 @@
         <v>86</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10196,7 +10201,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10226,10 +10231,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationObservation.xlsx
+++ b/docs/StructureDefinition-ImmunizationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
